--- a/data/source/grammar.xlsx
+++ b/data/source/grammar.xlsx
@@ -398,7 +398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="10" min="1" max="1"/>
@@ -3052,13 +3052,1513 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="10"/>
-    <row r="26" ht="15.75" customHeight="1" s="10"/>
-    <row r="27" ht="15.75" customHeight="1" s="10"/>
-    <row r="28" ht="15.75" customHeight="1" s="10"/>
-    <row r="29" ht="15.75" customHeight="1" s="10"/>
-    <row r="30" ht="15.75" customHeight="1" s="10"/>
-    <row r="31" ht="15.75" customHeight="1" s="10"/>
+    <row r="25" ht="15.75" customHeight="1" s="10">
+      <c r="A25" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>Будущее предположительное время (-r / -ar)</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>Будущее предположительное время образуется так: основа глагола + -r (после гласного) или -ar (после согласного) + личный аффикс: oʻqirman, borarman. Оно выражает вероятное, не вполне уверенное будущее действие, а также обещание: Ertaga borarman — «Завтра, наверное, пойду». Отрицание образуется аффиксом -mas: bormasman — «наверное, не пойду». В отличие от формы на -a/-y (boraman — «пойду»), эта форма звучит менее категорично.</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>Kelasi zamon gumon feʼli shunday yasaladi: feʼl negizi + -r (unlidan keyin) yoki -ar (undoshdan keyin) + shaxs-son qoʻshimchasi: oʻqirman, borarman. U ehtimol qilingan, toʻliq aniq boʻlmagan kelasi harakatni, shuningdek, vaʼdani bildiradi: Ertaga borarman. Boʻlishsiz shakli -mas qoʻshimchasi bilan yasaladi: bormasman. -a/-y shaklidan (boraman) farqli oʻlaroq, bu shakl qatʼiy emas, yumshoqroq eshitiladi.</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>The presumptive future is formed as follows: verb stem + -r (after a vowel) or -ar (after a consonant) + personal ending: oʻqirman, borarman. It expresses a probable, not entirely certain future action, and also a promise: Ertaga borarman — «I will probably go tomorrow». The negative is formed with the suffix -mas: bormasman — «I probably won't go». Unlike the -a/-y form (boraman — «I will go»), this form sounds less categorical.</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>Узбекский глагол имеет несколько форм будущего. Форма на -a/-y (boraman) сообщает о будущем как о решённом деле. Форма на -r/-ar называется kelasi zamon gumon feʼli — будущее предположительное время. Говорящий допускает, что действие произойдёт, но не утверждает это твёрдо. Поэтому рядом с ней часто стоят слова balki («может быть»), ehtimol («вероятно»), а в обещаниях — albatta («обязательно»).
+Образование: основа + -r, если основа оканчивается на гласный (oʻqi- → oʻqir, ishla- → ishlar); основа + -ar, если основа оканчивается на согласный (bor- → borar, yoz- → yozar, kel- → kelar). Затем добавляются личные аффиксы сказуемого: -man, -san, — (без аффикса), -miz, -siz, -(lar).
+Утвердительная форма (bormoq):
+men borarman — я, наверное, пойду
+sen borarsan — ты, наверное, пойдёшь
+u borar — он, наверное, пойдёт
+biz borarmiz — мы, наверное, пойдём
+siz borarsiz — вы, наверное, пойдёте
+ular borar(lar) — они, наверное, пойдут
+Основа на гласный (oʻqimoq): men oʻqirman, sen oʻqirsan, u oʻqir, biz oʻqirmiz, siz oʻqirsiz, ular oʻqir(lar).
+Отрицательная форма образуется аффиксом -mas, который ставится прямо после основы вместо -r/-ar:
+men bormasman — я, наверное, не пойду
+sen bormassan — ты, наверное, не пойдёшь
+u bormas — он, наверное, не пойдёт
+biz bormasmiz — мы, наверное, не пойдём
+siz bormassiz — вы, наверное, не пойдёте
+ular bormas(lar) — они, наверное, не пойдут
+Так же от основы на гласный: oʻqimasman, oʻqimassan, oʻqimas.
+Значения. 1) Вероятное будущее: Ertaga yomgʻir yogʻar — «Завтра, наверное, пойдёт дождь». 2) Обещание или мягкое согласие: Albatta qoʻngʻiroq qilarman — «Обязательно позвоню».
+Сравните: Ertaga boraman — «Завтра пойду» (уверенно); Ertaga borarman — «Завтра, наверное, пойду» (с долей сомнения).
+Обратите внимание: та же основа с -r/-ar входит в составную форму -ar edi (borar edim), о которой рассказано в темах 24 и 25.
+Примеры:
+Balki kechqurun kelarman. — Может быть, я приду вечером.
+Ehtimol, u bu kitobni oʻqir. — Вероятно, он прочитает эту книгу.
+Albatta xat yozarman. — Обязательно напишу письмо.
+Biz bu yil Samarqandga borarmiz. — В этом году мы, наверное, поедем в Самарканд.
+U bugun kelmas. — Он сегодня, наверное, не придёт.
+Men bu gapni unutmasman. — Я этих слов не забуду.</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>Oʻzbek feʼlida kelasi zamonning bir necha shakli bor. -a/-y shakli (boraman) kelasi harakatni hal qilingan ish sifatida xabar qiladi. -r/-ar shakli kelasi zamon gumon feʼli deyiladi. Soʻzlovchi harakat roʻy berishini taxmin qiladi, lekin buni qatʼiy tasdiqlamaydi. Shuning uchun bu shakl bilan koʻpincha balki, ehtimol soʻzlari, vaʼdalarda esa albatta soʻzi keladi.
+Yasalishi: negiz unli bilan tugasa, -r qoʻshiladi (oʻqi- → oʻqir, ishla- → ishlar); negiz undosh bilan tugasa, -ar qoʻshiladi (bor- → borar, yoz- → yozar, kel- → kelar). Keyin kesimlik qoʻshimchalari qoʻshiladi: -man, -san, — (qoʻshimchasiz), -miz, -siz, -(lar).
+Boʻlishli shakl (bormoq):
+men borarman — men (ehtimol) boraman
+sen borarsan — sen (ehtimol) borasan
+u borar — u (ehtimol) boradi
+biz borarmiz — biz (ehtimol) boramiz
+siz borarsiz — siz (ehtimol) borasiz
+ular borar(lar) — ular (ehtimol) boradi
+Unli bilan tugagan negiz (oʻqimoq): men oʻqirman, sen oʻqirsan, u oʻqir, biz oʻqirmiz, siz oʻqirsiz, ular oʻqir(lar).
+Boʻlishsiz shakl -r/-ar oʻrniga bevosita negizga qoʻshiladigan -mas qoʻshimchasi bilan yasaladi:
+men bormasman — men (ehtimol) bormayman
+sen bormassan — sen (ehtimol) bormaysan
+u bormas — u (ehtimol) bormaydi
+biz bormasmiz — biz (ehtimol) bormaymiz
+siz bormassiz — siz (ehtimol) bormaysiz
+ular bormas(lar) — ular (ehtimol) bormaydi
+Unli bilan tugagan negizdan ham xuddi shunday: oʻqimasman, oʻqimassan, oʻqimas.
+Maʼnolari. 1) Ehtimol qilingan kelasi harakat: Ertaga yomgʻir yogʻar. 2) Vaʼda yoki yumshoq rozilik: Albatta qoʻngʻiroq qilarman.
+Taqqoslang: Ertaga boraman — ishonch bilan aytilgan; Ertaga borarman — biroz shubha bilan aytilgan.
+Bu shakl soʻzlashuvda ham, badiiy adabiyotda ham koʻp uchraydi. U kelasi zamonning boshqa shakllaridan ohangi bilan farq qiladi: soʻzlovchi oʻz fikrini yumshoq, ehtiyotkorlik bilan bildiradi. Shuning uchun suhbatdoshga aniq vaʼda berishni istamaganda ham shu shakl qoʻllanadi.
+Eʼtibor bering: -r/-ar qoʻshimchali shu shakl -ar edi tarkibli shaklda ham qatnashadi (borar edim). Bu haqda 24- va 25-mavzularda soʻz boradi.
+Misollar:
+Balki kechqurun kelarman.
+Ehtimol, u bu kitobni oʻqir.
+Albatta xat yozarman.
+Biz bu yil Samarqandga borarmiz.
+U bugun kelmas.
+Men bu gapni unutmasman.</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>The Uzbek verb has several future forms. The -a/-y form (boraman) presents the future as a settled matter. The -r/-ar form is called kelasi zamon gumon feʼli — the presumptive future. The speaker assumes the action will happen but does not state it firmly. That is why it is often accompanied by the words balki («maybe»), ehtimol («probably») and, in promises, albatta («certainly»).
+Formation: stem + -r if the stem ends in a vowel (oʻqi- → oʻqir, ishla- → ishlar); stem + -ar if the stem ends in a consonant (bor- → borar, yoz- → yozar, kel- → kelar). Then the predicative personal endings are added: -man, -san, — (no ending), -miz, -siz, -(lar).
+Affirmative (bormoq):
+men borarman — I will probably go
+sen borarsan — you will probably go
+u borar — he/she will probably go
+biz borarmiz — we will probably go
+siz borarsiz — you (pl./polite) will probably go
+ular borar(lar) — they will probably go
+Vowel stem (oʻqimoq): men oʻqirman, sen oʻqirsan, u oʻqir, biz oʻqirmiz, siz oʻqirsiz, ular oʻqir(lar).
+The negative is formed with the suffix -mas, attached directly to the stem in place of -r/-ar:
+men bormasman — I probably won't go
+sen bormassan — you probably won't go
+u bormas — he/she probably won't go
+biz bormasmiz — we probably won't go
+siz bormassiz — you (pl./polite) probably won't go
+ular bormas(lar) — they probably won't go
+The same from a vowel stem: oʻqimasman, oʻqimassan, oʻqimas.
+Meanings. 1) A probable future: Ertaga yomgʻir yogʻar — «It will probably rain tomorrow». 2) A promise or mild agreement: Albatta qoʻngʻiroq qilarman — «I'll call for sure».
+Compare: Ertaga boraman — «I will go tomorrow» (confident); Ertaga borarman — «I'll probably go tomorrow» (with some doubt).
+Note: the same stem with -r/-ar appears in the compound form -ar edi (borar edim), covered in topics 24 and 25.
+Examples:
+Balki kechqurun kelarman. — Maybe I'll come in the evening.
+Ehtimol, u bu kitobni oʻqir. — He will probably read this book.
+Albatta xat yozarman. — I'll write a letter for sure.
+Biz bu yil Samarqandga borarmiz. — We'll probably go to Samarkand this year.
+U bugun kelmas. — He probably won't come today.
+Men bu gapni unutmasman. — I won't forget these words.</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте все личные формы будущего предположительного времени от глаголов kelmoq и ishlamoq (утвердительные и отрицательные).</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>Kelmoq va ishlamoq feʼllarini kelasi zamon gumon feʼli shaklida turlang (boʻlishli va boʻlishsiz).</t>
+        </is>
+      </c>
+      <c r="L25" s="0" t="inlineStr">
+        <is>
+          <t>Conjugate kelmoq and ishlamoq in all persons of the presumptive future (affirmative and negative).</t>
+        </is>
+      </c>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t>Поставьте в отрицание: Men borarman. U yozar. Biz oʻqirmiz. Siz kelarsiz.</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>Boʻlishsiz shaklga qoʻying: Men borarman. U yozar. Biz oʻqirmiz. Siz kelarsiz.</t>
+        </is>
+      </c>
+      <c r="O25" s="0" t="inlineStr">
+        <is>
+          <t>Make negative: Men borarman. U yozar. Biz oʻqirmiz. Siz kelarsiz.</t>
+        </is>
+      </c>
+      <c r="P25" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Может быть, я приду завтра. Он, наверное, не позвонит. Обязательно напишу вам.</t>
+        </is>
+      </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Balki ertaga kelarman. U, ehtimol, qoʻngʻiroq qilmas. Sizga albatta yozarman.</t>
+        </is>
+      </c>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t>Translate: Maybe I'll come tomorrow. He probably won't call. I'll certainly write to you.</t>
+        </is>
+      </c>
+      <c r="S25" s="0" t="inlineStr">
+        <is>
+          <t>Объясните разницу между Ertaga boraman и Ertaga borarman и составьте свою пару таких предложений.</t>
+        </is>
+      </c>
+      <c r="T25" s="0" t="inlineStr">
+        <is>
+          <t>Ertaga boraman va Ertaga borarman gaplari orasidagi farqni tushuntiring va shunday juftlikdan birini oʻzingiz tuzing.</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="inlineStr">
+        <is>
+          <t>Explain the difference between Ertaga boraman and Ertaga borarman and make up a similar pair of your own.</t>
+        </is>
+      </c>
+      <c r="V25" s="0" t="inlineStr">
+        <is>
+          <t>Составьте короткий диалог: друг приглашает вас в гости, а вы не уверены, что сможете прийти (используйте balki, ehtimol и формы на -r/-ar, -mas).</t>
+        </is>
+      </c>
+      <c r="W25" s="0" t="inlineStr">
+        <is>
+          <t>Qisqa suhbat tuzing: doʻstingiz sizni mehmonga taklif qiladi, siz esa kela olishingizga ishonchingiz komil emas (balki, ehtimol soʻzlari va -r/-ar, -mas shakllaridan foydalaning).</t>
+        </is>
+      </c>
+      <c r="X25" s="0" t="inlineStr">
+        <is>
+          <t>Write a short dialogue: a friend invites you over, and you are not sure you can come (use balki, ehtimol and the -r/-ar and -mas forms).</t>
+        </is>
+      </c>
+      <c r="Y25" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="10">
+      <c r="A26" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>Будущее время намерения (-moqchi)</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>Будущее время намерения образуется так: основа глагола + -moqchi + личный аффикс: bormoqchiman — «я собираюсь пойти, хочу пойти». Аффикс -moqchi одинаков после гласного и после согласного: oʻqimoqchiman, yozmoqchiman. Отрицание образуется словом emas с личным аффиксом: bormoqchi emasman — «я не собираюсь идти». Форма выражает намерение, план, желание совершить действие.</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>Kelasi zamon maqsad feʼli shunday yasaladi: feʼl negizi + -moqchi + shaxs-son qoʻshimchasi: bormoqchiman. -moqchi qoʻshimchasi unlidan keyin ham, undoshdan keyin ham bir xil: oʻqimoqchiman, yozmoqchiman. Boʻlishsiz shakli shaxs qoʻshimchasini olgan emas soʻzi bilan yasaladi: bormoqchi emasman. Bu shakl harakatni bajarish niyati, rejasi, istagini bildiradi.</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>The future of intention is formed as follows: verb stem + -moqchi + personal ending: bormoqchiman — «I am going to go, I want to go». The suffix -moqchi is the same after a vowel and after a consonant: oʻqimoqchiman, yozmoqchiman. The negative is formed with the word emas carrying the personal ending: bormoqchi emasman — «I am not going to go». The form expresses an intention, a plan, a wish to perform the action.</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>Форма на -moqchi (kelasi zamon maqsad feʼli) говорит не о самом будущем действии, а о намерении его совершить. По-русски она переводится словами «собираюсь», «хочу», «намерен»: Men shifokor boʻlmoqchiman — «Я хочу стать врачом».
+Образование: основа глагола + -moqchi + личные аффиксы сказуемого -man, -san, —, -miz, -siz, -(lar). Аффикс не меняется в зависимости от того, на что оканчивается основа: bor- → bormoqchi, oʻqi- → oʻqimoqchi, ishla- → ishlamoqchi. Запомнить легко: это инфинитив на -moq плюс -chi.
+Утвердительная форма (bormoq):
+men bormoqchiman — я собираюсь пойти
+sen bormoqchisan — ты собираешься пойти
+u bormoqchi — он собирается пойти
+biz bormoqchimiz — мы собираемся пойти
+siz bormoqchisiz — вы собираетесь пойти
+ular bormoqchi(lar) — они собираются пойти
+Основа на гласный (oʻqimoq): men oʻqimoqchiman, sen oʻqimoqchisan, u oʻqimoqchi, biz oʻqimoqchimiz, siz oʻqimoqchisiz, ular oʻqimoqchi(lar).
+Отрицательная форма образуется не аффиксом -ma, а отдельным словом emas («не»), к которому переходит личный аффикс:
+men bormoqchi emasman — я не собираюсь идти
+sen bormoqchi emassan — ты не собираешься идти
+u bormoqchi emas — он не собирается идти
+biz bormoqchi emasmiz — мы не собираемся идти
+siz bormoqchi emassiz — вы не собираетесь идти
+ular bormoqchi emas(lar) — они не собираются идти
+Общий вопрос образуется частицей -mi, которая ставится перед личным аффиксом: Kinoga bormoqchimisiz? — «Вы собираетесь в кино?» В вопросе с вопросительным словом частица не нужна: Qayerga bormoqchisiz? — «Куда вы собираетесь?»
+Прошедшее намерение передаётся с edi: bormoqchi edim — «я собирался пойти». Так часто говорят о неосуществлённом плане: Bormoqchi edim, lekin vaqtim boʻlmadi — «Я собирался пойти, но у меня не было времени».
+Сравните три формы будущего: boraman — «пойду» (уверенно), borarman — «наверное, пойду», bormoqchiman — «собираюсь пойти» (намерение).
+Примеры:
+Men oʻzbek tilini oʻrganmoqchiman. — Я хочу выучить узбекский язык.
+Ertaga bozorga bormoqchimiz. — Завтра мы собираемся пойти на базар.
+U yangi uy sotib olmoqchi. — Он собирается купить новый дом.
+Men bugun televizor koʻrmoqchi emasman. — Я сегодня не собираюсь смотреть телевизор.
+Nima qilmoqchisiz? — Что вы собираетесь делать?
+Ular dam olishga bormoqchi edi. — Они собирались поехать отдыхать.</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>-moqchi shakli (kelasi zamon maqsad feʼli) kelasi harakatning oʻzini emas, balki uni bajarish niyatini bildiradi. Rus tiliga «собираюсь», «хочу», «намерен» soʻzlari bilan tarjima qilinadi: Men shifokor boʻlmoqchiman.
+Yasalishi: feʼl negizi + -moqchi + kesimlik qoʻshimchalari -man, -san, —, -miz, -siz, -(lar). Qoʻshimcha negiz qanday tovush bilan tugashiga qarab oʻzgarmaydi: bor- → bormoqchi, oʻqi- → oʻqimoqchi, ishla- → ishlamoqchi. Eslab qolish oson: bu -moq bilan tugagan harakat nomi va -chi qoʻshimchasi.
+Boʻlishli shakl (bormoq):
+men bormoqchiman — men borish niyatidaman
+sen bormoqchisan — sen borish niyatidasan
+u bormoqchi — u borish niyatida
+biz bormoqchimiz — biz borish niyatidamiz
+siz bormoqchisiz — siz borish niyatidasiz
+ular bormoqchi(lar) — ular borish niyatida
+Unli bilan tugagan negiz (oʻqimoq): men oʻqimoqchiman, sen oʻqimoqchisan, u oʻqimoqchi, biz oʻqimoqchimiz, siz oʻqimoqchisiz, ular oʻqimoqchi(lar).
+Boʻlishsiz shakl -ma qoʻshimchasi bilan emas, balki alohida emas soʻzi bilan yasaladi; shaxs qoʻshimchasi shu soʻzga qoʻshiladi:
+men bormoqchi emasman — men borish niyatida emasman
+sen bormoqchi emassan — sen borish niyatida emassan
+u bormoqchi emas — u borish niyatida emas
+biz bormoqchi emasmiz — biz borish niyatida emasmiz
+siz bormoqchi emassiz — siz borish niyatida emassiz
+ular bormoqchi emas(lar) — ular borish niyatida emas
+Umumiy soʻroq -mi yuklamasi bilan yasaladi, u shaxs qoʻshimchasidan oldin keladi: Kinoga bormoqchimisiz? Soʻroq soʻzi bor gapda yuklama kerak emas: Qayerga bormoqchisiz?
+Oʻtgan zamondagi niyat edi bilan ifodalanadi: bormoqchi edim. Bu shakl koʻpincha amalga oshmagan reja haqida gapirganda ishlatiladi: Bormoqchi edim, lekin vaqtim boʻlmadi.
+Bu shakl kundalik nutqda juda koʻp ishlatiladi: doʻkonda, mehmonxonada, ish joyida oʻz istagingizni aytish uchun qulay. Masalan, Men xona band qilmoqchiman yoki Men chipta olmoqchiman deyish mumkin.
+Kelasi zamonning uch shaklini taqqoslang: boraman — ishonch bilan, borarman — taxmin bilan, bormoqchiman — niyat.
+Misollar:
+Men oʻzbek tilini oʻrganmoqchiman.
+Ertaga bozorga bormoqchimiz.
+U yangi uy sotib olmoqchi.
+Men bugun televizor koʻrmoqchi emasman.
+Nima qilmoqchisiz?
+Ular dam olishga bormoqchi edi.</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>The -moqchi form (kelasi zamon maqsad feʼli) speaks not about the future action itself but about the intention to perform it. In English it is rendered as «I am going to», «I want to», «I intend to»: Men shifokor boʻlmoqchiman — «I want to become a doctor».
+Formation: verb stem + -moqchi + the predicative personal endings -man, -san, —, -miz, -siz, -(lar). The suffix does not change depending on how the stem ends: bor- → bormoqchi, oʻqi- → oʻqimoqchi, ishla- → ishlamoqchi. It is easy to remember: it is the -moq infinitive plus -chi.
+Affirmative (bormoq):
+men bormoqchiman — I am going to go
+sen bormoqchisan — you are going to go
+u bormoqchi — he/she is going to go
+biz bormoqchimiz — we are going to go
+siz bormoqchisiz — you (pl./polite) are going to go
+ular bormoqchi(lar) — they are going to go
+Vowel stem (oʻqimoq): men oʻqimoqchiman, sen oʻqimoqchisan, u oʻqimoqchi, biz oʻqimoqchimiz, siz oʻqimoqchisiz, ular oʻqimoqchi(lar).
+The negative is formed not with the suffix -ma but with the separate word emas («not»), which takes the personal ending:
+men bormoqchi emasman — I am not going to go
+sen bormoqchi emassan — you are not going to go
+u bormoqchi emas — he/she is not going to go
+biz bormoqchi emasmiz — we are not going to go
+siz bormoqchi emassiz — you (pl./polite) are not going to go
+ular bormoqchi emas(lar) — they are not going to go
+A yes/no question is formed with the particle -mi, placed before the personal ending: Kinoga bormoqchimisiz? — «Are you going to the cinema?» With a question word the particle is not needed: Qayerga bormoqchisiz? — «Where are you going to go?»
+A past intention is expressed with edi: bormoqchi edim — «I was going to go». This is often said about a plan that did not happen: Bormoqchi edim, lekin vaqtim boʻlmadi — «I was going to go, but I had no time».
+Compare the three future forms: boraman — «I will go» (confident), borarman — «I'll probably go», bormoqchiman — «I am going to go» (intention).
+Examples:
+Men oʻzbek tilini oʻrganmoqchiman. — I want to learn Uzbek.
+Ertaga bozorga bormoqchimiz. — Tomorrow we are going to go to the bazaar.
+U yangi uy sotib olmoqchi. — He is going to buy a new house.
+Men bugun televizor koʻrmoqchi emasman. — I am not going to watch TV today.
+Nima qilmoqchisiz? — What are you going to do?
+Ular dam olishga bormoqchi edi. — They were going to go on holiday.</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте все личные формы с -moqchi от глаголов yozmoq и ishlamoq, затем поставьте их в отрицание с emas.</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>Yozmoq va ishlamoq feʼllaridan -moqchi bilan barcha shaxs shakllarini yasang, soʻng ularni emas bilan boʻlishsiz shaklga qoʻying.</t>
+        </is>
+      </c>
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>Form all persons with -moqchi from yozmoq and ishlamoq, then make them negative with emas.</t>
+        </is>
+      </c>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Я хочу выучить узбекский язык. Мы собираемся поехать в Бухару. Он не собирается работать сегодня.</t>
+        </is>
+      </c>
+      <c r="N26" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Men oʻzbek tilini oʻrganmoqchiman. Biz Buxoroga bormoqchimiz. U bugun ishlamoqchi emas.</t>
+        </is>
+      </c>
+      <c r="O26" s="0" t="inlineStr">
+        <is>
+          <t>Translate: I want to learn Uzbek. We are going to go to Bukhara. He is not going to work today.</t>
+        </is>
+      </c>
+      <c r="P26" s="0" t="inlineStr">
+        <is>
+          <t>Задайте общий вопрос к предложениям: Siz kinoga bormoqchisiz. Ular uy sotib olmoqchi.</t>
+        </is>
+      </c>
+      <c r="Q26" s="0" t="inlineStr">
+        <is>
+          <t>Gaplarga umumiy soʻroq bering: Siz kinoga bormoqchisiz. Ular uy sotib olmoqchi.</t>
+        </is>
+      </c>
+      <c r="R26" s="0" t="inlineStr">
+        <is>
+          <t>Turn into yes/no questions: Siz kinoga bormoqchisiz. Ular uy sotib olmoqchi.</t>
+        </is>
+      </c>
+      <c r="S26" s="0" t="inlineStr">
+        <is>
+          <t>Составьте три предложения о неосуществлённых планах по образцу: Bormoqchi edim, lekin vaqtim boʻlmadi.</t>
+        </is>
+      </c>
+      <c r="T26" s="0" t="inlineStr">
+        <is>
+          <t>Amalga oshmagan rejalar haqida namunadagidek uchta gap tuzing: Bormoqchi edim, lekin vaqtim boʻlmadi.</t>
+        </is>
+      </c>
+      <c r="U26" s="0" t="inlineStr">
+        <is>
+          <t>Write three sentences about plans that did not happen, following the model: Bormoqchi edim, lekin vaqtim boʻlmadi.</t>
+        </is>
+      </c>
+      <c r="V26" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог «Планы на выходные»: спросите собеседника Nima qilmoqchisiz? и расскажите о своих планах.</t>
+        </is>
+      </c>
+      <c r="W26" s="0" t="inlineStr">
+        <is>
+          <t>«Dam olish kunlari rejalari» mavzusida suhbat tuzing: suhbatdoshingizdan Nima qilmoqchisiz? deb soʻrang va oʻz rejalaringiz haqida gapiring.</t>
+        </is>
+      </c>
+      <c r="X26" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue «Weekend plans»: ask your partner Nima qilmoqchisiz? and talk about your own plans.</t>
+        </is>
+      </c>
+      <c r="Y26" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="10">
+      <c r="A27" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>Условное наклонение (-sa)</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>Условное наклонение образуется так: основа глагола + -sa + личный аффикс: borsam, borsang, borsa, borsak, borsangiz, borsalar. Оно отвечает русскому «если…»: Vaqtim boʻlsa, boraman — «Если у меня будет время, пойду». Часто в начале условной части стоит слово agar («если»), но условие выражает именно аффикс -sa. Отрицание образуется аффиксом -ma перед -sa: bormasam — «если я не пойду».</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>Shart mayli shunday yasaladi: feʼl negizi + -sa + shaxs-son qoʻshimchasi: borsam, borsang, borsa, borsak, borsangiz, borsalar. U rus tilidagi «если…» ga mos keladi: Vaqtim boʻlsa, boraman. Shart qismining boshida koʻpincha agar soʻzi turadi, lekin shartni aynan -sa qoʻshimchasi ifodalaydi. Boʻlishsiz shakli -sa dan oldin -ma qoʻshimchasi bilan yasaladi: bormasam.</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>The conditional mood is formed as follows: verb stem + -sa + personal ending: borsam, borsang, borsa, borsak, borsangiz, borsalar. It corresponds to English «if…»: Vaqtim boʻlsa, boraman — «If I have time, I'll go». The word agar («if») often stands at the start of the condition, but it is the suffix -sa that actually expresses the condition. The negative is formed with -ma before -sa: bormasam — «if I don't go».</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>Shart mayli — условное наклонение. Оно называет условие, при котором произойдёт другое действие. Часть с -sa стоит первой, главная часть — после неё: Yomgʻir yogʻsa, uyda qolamiz — «Если пойдёт дождь, останемся дома».
+Образование: основа + -sa + личные аффиксы притяжательного типа (те же, что в прошедшем времени на -di): -m, -ng, —, -k, -ngiz, -lar. Аффикс -sa не меняется после гласного и согласного.
+Утвердительная форма (bormoq):
+men borsam — если я пойду
+sen borsang — если ты пойдёшь
+u borsa — если он пойдёт
+biz borsak — если мы пойдём
+siz borsangiz — если вы пойдёте
+ular borsalar — если они пойдут (в речи часто просто borsa)
+Основа на гласный (oʻqimoq): oʻqisam, oʻqisang, oʻqisa, oʻqisak, oʻqisangiz, oʻqisalar.
+Отрицательная форма: основа + -ma + -sa + личный аффикс:
+men bormasam — если я не пойду
+sen bormasang — если ты не пойдёшь
+u bormasa — если он не пойдёт
+biz bormasak — если мы не пойдём
+siz bormasangiz — если вы не пойдёте
+ular bormasalar — если они не пойдут
+Слово agar. Союз agar («если») ставится в начале условной части, но он необязателен, а аффикс -sa обязателен: Agar vaqtingiz boʻlsa, keling = Vaqtingiz boʻlsa, keling — «Если у вас будет время, приходите». Без -sa условия нет, даже если есть agar.
+Условие без глагола. Если в условии нет действия (слова bor «есть», yoʻq «нет», kerak «нужно» или существительное), к нему добавляют boʻlsa — форму глагола boʻlmoq: Pulim boʻlsa, mashina olaman — «Если у меня будут деньги, куплю машину». Kerak boʻlsa, qoʻngʻiroq qiling — «Если нужно, позвоните».
+Время в условной части не выражается: borsam может значить и «если я пойду», и «когда я пойду». Время показывает главная часть: Uyga borsam, qoʻngʻiroq qilaman — «Когда приду домой, позвоню».
+Дополнительные значения:
+-sa ham — «даже если, хотя»: Charchasam ham, ishlayman — «Даже если устану, буду работать».
+-sa boʻladimi? — вежливая просьба о разрешении: Kirsam boʻladimi? — «Можно войти?»
+Примеры:
+Agar ertaga havo yaxshi boʻlsa, toqqa boramiz. — Если завтра будет хорошая погода, поедем в горы.
+Bu kitobni oʻqisangiz, sizga yoqadi. — Если вы прочитаете эту книгу, она вам понравится.
+Tez yursak, poyezdga ulguramiz. — Если пойдём быстро, успеем на поезд.
+Dorini ichmasang, tuzalmaysan. — Если не будешь пить лекарство, не поправишься.
+Savolingiz boʻlsa, soʻrang. — Если у вас есть вопрос, спрашивайте.
+Kirsam boʻladimi? — Можно войти?</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>Shart mayli boshqa harakat roʻy berishi uchun zarur boʻlgan shartni bildiradi. -sa qoʻshimchali qism oldin, bosh qism undan keyin keladi: Yomgʻir yogʻsa, uyda qolamiz.
+Yasalishi: negiz + -sa + egalik tipidagi shaxs-son qoʻshimchalari (-di bilan yasalgan oʻtgan zamondagi kabi): -m, -ng, —, -k, -ngiz, -lar. -sa qoʻshimchasi unli va undoshdan keyin oʻzgarmaydi.
+Boʻlishli shakl (bormoq):
+men borsam — agar men borsam
+sen borsang — agar sen borsang
+u borsa — agar u borsa
+biz borsak — agar biz borsak
+siz borsangiz — agar siz borsangiz
+ular borsalar — agar ular borsa (ogʻzaki nutqda koʻpincha borsa)
+Unli bilan tugagan negiz (oʻqimoq): oʻqisam, oʻqisang, oʻqisa, oʻqisak, oʻqisangiz, oʻqisalar.
+Boʻlishsiz shakl: negiz + -ma + -sa + shaxs-son qoʻshimchasi:
+men bormasam — agar men bormasam
+sen bormasang — agar sen bormasang
+u bormasa — agar u bormasa
+biz bormasak — agar biz bormasak
+siz bormasangiz — agar siz bormasangiz
+ular bormasalar — agar ular bormasa
+Agar soʻzi. Agar bogʻlovchisi shart qismining boshida keladi, lekin u majburiy emas, -sa qoʻshimchasi esa majburiy: Agar vaqtingiz boʻlsa, keling = Vaqtingiz boʻlsa, keling. Agar boʻlsa ham, -sa boʻlmasa, shart ifodalanmaydi.
+Feʼlsiz shart. Shartda harakat boʻlmasa (bor, yoʻq, kerak soʻzlari yoki ot), unga boʻlmoq feʼlining boʻlsa shakli qoʻshiladi: Pulim boʻlsa, mashina olaman. Kerak boʻlsa, qoʻngʻiroq qiling.
+Shart qismida zamon ifodalanmaydi: borsam ham «если я пойду», ham «когда я пойду» maʼnosini berishi mumkin. Zamonni bosh qism koʻrsatadi: Uyga borsam, qoʻngʻiroq qilaman.
+Qoʻshimcha maʼnolar:
+-sa ham — «hatto … boʻlsa ham» maʼnosi: Charchasam ham, ishlayman.
+-sa boʻladimi? — ruxsat soʻrashning hurmatli shakli: Kirsam boʻladimi?
+Shart maylidagi feʼl shart qismining oxirida turadi va undan keyin vergul qoʻyiladi. Bosh qismdagi feʼl odatda hozirgi-kelasi zamonda yoki buyruq maylida boʻladi: boramiz, keling, soʻrang.
+Shunday qilib, shart maylida eng muhim belgi -sa qoʻshimchasidir, agar soʻzi esa faqat shartni kuchaytiradi.
+Misollar:
+Agar ertaga havo yaxshi boʻlsa, toqqa boramiz.
+Bu kitobni oʻqisangiz, sizga yoqadi.
+Tez yursak, poyezdga ulguramiz.
+Dorini ichmasang, tuzalmaysan.
+Savolingiz boʻlsa, soʻrang.
+Kirsam boʻladimi?</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>Shart mayli is the conditional mood. It names a condition under which another action will take place. The -sa clause comes first, the main clause after it: Yomgʻir yogʻsa, uyda qolamiz — «If it rains, we'll stay at home».
+Formation: stem + -sa + the possessive-type personal endings (the same as in the -di past): -m, -ng, —, -k, -ngiz, -lar. The suffix -sa does not change after vowels or consonants.
+Affirmative (bormoq):
+men borsam — if I go
+sen borsang — if you go
+u borsa — if he/she goes
+biz borsak — if we go
+siz borsangiz — if you (pl./polite) go
+ular borsalar — if they go (in speech often just borsa)
+Vowel stem (oʻqimoq): oʻqisam, oʻqisang, oʻqisa, oʻqisak, oʻqisangiz, oʻqisalar.
+Negative: stem + -ma + -sa + personal ending:
+men bormasam — if I don't go
+sen bormasang — if you don't go
+u bormasa — if he/she doesn't go
+biz bormasak — if we don't go
+siz bormasangiz — if you (pl./polite) don't go
+ular bormasalar — if they don't go
+The word agar. The conjunction agar («if») stands at the start of the condition, but it is optional, while the suffix -sa is obligatory: Agar vaqtingiz boʻlsa, keling = Vaqtingiz boʻlsa, keling — «If you have time, come over». Without -sa there is no condition, even if agar is present.
+A condition without a verb. If the condition contains no action (the words bor «there is», yoʻq «there isn't», kerak «necessary», or a noun), boʻlsa — a form of the verb boʻlmoq — is added: Pulim boʻlsa, mashina olaman — «If I have money, I'll buy a car». Kerak boʻlsa, qoʻngʻiroq qiling — «Call if necessary».
+Tense is not expressed in the conditional clause: borsam can mean both «if I go» and «when I go». The main clause shows the time: Uyga borsam, qoʻngʻiroq qilaman — «When I get home, I'll call».
+Additional meanings:
+-sa ham — «even if, although»: Charchasam ham, ishlayman — «Even if I get tired, I'll keep working».
+-sa boʻladimi? — a polite request for permission: Kirsam boʻladimi? — «May I come in?»
+Examples:
+Agar ertaga havo yaxshi boʻlsa, toqqa boramiz. — If the weather is good tomorrow, we'll go to the mountains.
+Bu kitobni oʻqisangiz, sizga yoqadi. — If you read this book, you'll like it.
+Tez yursak, poyezdga ulguramiz. — If we walk fast, we'll catch the train.
+Dorini ichmasang, tuzalmaysan. — If you don't take the medicine, you won't get better.
+Savolingiz boʻlsa, soʻrang. — If you have a question, ask.
+Kirsam boʻladimi? — May I come in?</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте условные формы (утвердительные и отрицательные) во всех лицах от глаголов kelmoq и ishlamoq.</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>Kelmoq va ishlamoq feʼllaridan barcha shaxslarda shart maylining boʻlishli va boʻlishsiz shakllarini yasang.</t>
+        </is>
+      </c>
+      <c r="L27" s="0" t="inlineStr">
+        <is>
+          <t>Form the conditional (affirmative and negative) in all persons from kelmoq and ishlamoq.</t>
+        </is>
+      </c>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t>Соедините части в одно предложение с -sa: Vaqtim bor — kinoga boraman. Yomgʻir yogʻadi — uyda qolamiz. Siz kelasiz — xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="N27" s="0" t="inlineStr">
+        <is>
+          <t>Qismlarni -sa yordamida bitta gapga birlashtiring: Vaqtim bor — kinoga boraman. Yomgʻir yogʻadi — uyda qolamiz. Siz kelasiz — xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="O27" s="0" t="inlineStr">
+        <is>
+          <t>Join the parts into one sentence with -sa: Vaqtim bor — kinoga boraman. Yomgʻir yogʻadi — uyda qolamiz. Siz kelasiz — xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="P27" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Если вы не придёте, я позвоню. Если нужно, я помогу. Даже если устану, закончу работу.</t>
+        </is>
+      </c>
+      <c r="Q27" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Siz kelmasangiz, qoʻngʻiroq qilaman. Kerak boʻlsa, yordam beraman. Charchasam ham, ishni tugataman.</t>
+        </is>
+      </c>
+      <c r="R27" s="0" t="inlineStr">
+        <is>
+          <t>Translate: If you don't come, I'll call. If necessary, I'll help. Even if I get tired, I'll finish the work.</t>
+        </is>
+      </c>
+      <c r="S27" s="0" t="inlineStr">
+        <is>
+          <t>Поставьте условную часть в отрицание: Tez yursak, ulguramiz. Dorini ichsang, tuzalasan. Oʻqisangiz, bilasiz.</t>
+        </is>
+      </c>
+      <c r="T27" s="0" t="inlineStr">
+        <is>
+          <t>Shart qismini boʻlishsiz shaklga qoʻying: Tez yursak, ulguramiz. Dorini ichsang, tuzalasan. Oʻqisangiz, bilasiz.</t>
+        </is>
+      </c>
+      <c r="U27" s="0" t="inlineStr">
+        <is>
+          <t>Make the conditional clause negative: Tez yursak, ulguramiz. Dorini ichsang, tuzalasan. Oʻqisangiz, bilasiz.</t>
+        </is>
+      </c>
+      <c r="V27" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог в учреждении: вежливо попросите разрешения с помощью -sa boʻladimi? (войти, сесть, задать вопрос).</t>
+        </is>
+      </c>
+      <c r="W27" s="0" t="inlineStr">
+        <is>
+          <t>Muassasada boʻladigan suhbat tuzing: -sa boʻladimi? yordamida hurmat bilan ruxsat soʻrang (kirish, oʻtirish, savol berish).</t>
+        </is>
+      </c>
+      <c r="X27" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue at an office: politely ask for permission using -sa boʻladimi? (to come in, to sit down, to ask a question).</t>
+        </is>
+      </c>
+      <c r="Y27" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="10">
+      <c r="A28" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>Желание и нереальное условие (-sa edi, -ar edi, -gan boʻlardi)</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>Сослагательные значения («бы») в узбекском передаются тремя составными формами. Форма -sa edi выражает желание или нереальное условие: borsam edi — «вот бы я пошёл; если бы я пошёл». Форма -ar edi называет предполагаемый результат: borar edim — «я бы пошёл». Форма -gan boʻlardi говорит о результате, который мог бы наступить в прошлом: borgan boʻlardim — «я бы пошёл (тогда)».</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>Oʻzbek tilida istak va shart-natija maʼnolari uchta tarkibli shakl bilan ifodalanadi. -sa edi shakli istak yoki real boʻlmagan shartni bildiradi: borsam edi. -ar edi shakli taxmin qilingan natijani bildiradi: borar edim. -gan boʻlardi shakli oʻtmishda roʻy berishi mumkin boʻlgan natijani bildiradi: borgan boʻlardim.</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>Subjunctive meanings («would», «if only») are expressed in Uzbek by three compound forms. The -sa edi form expresses a wish or an unreal condition: borsam edi — «if only I went; if I went». The -ar edi form names the assumed result: borar edim — «I would go». The -gan boʻlardi form speaks of a result that could have happened in the past: borgan boʻlardim — «I would have gone (then)».</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>В узбекском нет отдельной частицы «бы». Её значения передаются составными формами, в которых участвует вспомогательный глагол edi или boʻlardi.
+1. Желание: -sa edi. Основа + -sa + личный аффикс + edi. Форма выражает мечту или сожаление: «вот бы…», «если бы…».
+men borsam edi — вот бы я пошёл
+sen borsang edi — вот бы ты пошёл
+u borsa edi — вот бы он пошёл
+biz borsak edi — вот бы мы пошли
+siz borsangiz edi — вот бы вы пошли
+ular borsalar edi — вот бы они пошли
+От основы на гласный: oʻqisam edi. Отрицание: bormasam edi — «лучше бы я не ходил, вот бы я не пошёл». В разговоре часто звучит слитно: borsaydim. Та же форма служит нереальным условием: Vaqtim boʻlsa edi, … — «Если бы у меня было время, …».
+2. Предполагаемый результат: -ar edi. Основа + -r/-ar + edi с личным аффиксом (edim, eding, edi, edik, edingiz, edilar).
+men borar edim — я бы пошёл
+sen borar eding — ты бы пошёл
+u borar edi — он бы пошёл
+biz borar edik — мы бы пошли
+siz borar edingiz — вы бы пошли
+ular borar edilar — они бы пошли
+От основы на гласный: oʻqir edim — «я бы прочитал». Отрицание: bormas edim — «я бы не пошёл». Вместе с -sa edi получается полное нереальное условие: Vaqtim boʻlsa edi, borar edim — «Если бы у меня было время, я бы пошёл». Заметьте: та же форма borar edim может значить «бывало, я ходил» (тема 25); значение подсказывает контекст.
+3. Нереальный результат в прошлом: -gan boʻlardi. Причастие на -gan + boʻlardi с личным аффиксом (boʻlardim, boʻlarding, boʻlardi, boʻlardik, boʻlardingiz, boʻlardilar).
+men borgan boʻlardim — я бы пошёл (тогда)
+sen borgan boʻlarding — ты бы пошёл (тогда)
+u borgan boʻlardi — он бы пошёл (тогда)
+biz borgan boʻlardik — мы бы пошли (тогда)
+siz borgan boʻlardingiz — вы бы пошли (тогда)
+ular borgan boʻlardilar — они бы пошли (тогда)
+От основы на гласный: oʻqigan boʻlardim. Отрицание: bormagan boʻlardim. Форма подчёркивает, что момент упущен: Oldinroq aytganingda, men ham borgan boʻlardim — «Если бы ты сказал раньше, я бы тоже пошёл».
+Итак: -sa edi — желание или условие «если бы»; -ar edi — «я бы сделал»; -gan boʻlardi — «я бы сделал тогда, но не сделал».
+Примеры:
+Pulim boʻlsa edi, uy olar edim. — Если бы у меня были деньги, я бы купил дом.
+Oʻzbek tilini yaxshi bilsam edi! — Вот бы мне хорошо знать узбекский!
+Sen kelsang edi, xursand boʻlar edim. — Если бы ты пришёл, я был бы рад.
+Bu kitobni oʻqisangiz edi, sizga yoqar edi. — Если бы вы прочитали эту книгу, она бы вам понравилась.
+Ertaroq chiqqanimizda, poyezdga ulgurgan boʻlardik. — Если бы мы вышли пораньше, мы бы успели на поезд.
+Bunday demasam edi. — Лучше бы я так не говорил.</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>Oʻzbek tilida rus tilidagi «бы» yuklamasiga toʻgʻri keladigan alohida soʻz yoʻq. Bu maʼnolar edi yoki boʻlardi yordamchi feʼli ishtirok etgan tarkibli shakllar bilan ifodalanadi.
+1. Istak: -sa edi. Negiz + -sa + shaxs-son qoʻshimchasi + edi. Bu shakl orzu yoki afsusni bildiradi.
+men borsam edi
+sen borsang edi
+u borsa edi
+biz borsak edi
+siz borsangiz edi
+ular borsalar edi
+Unli bilan tugagan negizdan: oʻqisam edi. Boʻlishsiz shakli: bormasam edi — afsus maʼnosida. Ogʻzaki nutqda koʻpincha qoʻshilib aytiladi: borsaydim. Shu shakl real boʻlmagan shartni ham bildiradi: Vaqtim boʻlsa edi, …
+2. Taxmin qilingan natija: -ar edi. Negiz + -r/-ar + shaxs-son qoʻshimchasini olgan edi (edim, eding, edi, edik, edingiz, edilar).
+men borar edim
+sen borar eding
+u borar edi
+biz borar edik
+siz borar edingiz
+ular borar edilar
+Unli bilan tugagan negizdan: oʻqir edim. Boʻlishsiz shakli: bormas edim. -sa edi bilan birga toʻliq real boʻlmagan shart hosil boʻladi: Vaqtim boʻlsa edi, borar edim. Eʼtibor bering: borar edim shakli «бывало, я ходил» maʼnosini ham berishi mumkin (25-mavzu); maʼnoni gap mazmuni koʻrsatadi.
+3. Oʻtmishdagi real boʻlmagan natija: -gan boʻlardi. -gan sifatdoshi + shaxs-son qoʻshimchasini olgan boʻlardi (boʻlardim, boʻlarding, boʻlardi, boʻlardik, boʻlardingiz, boʻlardilar).
+men borgan boʻlardim
+sen borgan boʻlarding
+u borgan boʻlardi
+biz borgan boʻlardik
+siz borgan boʻlardingiz
+ular borgan boʻlardilar
+Unli bilan tugagan negizdan: oʻqigan boʻlardim. Boʻlishsiz shakli: bormagan boʻlardim. Bu shakl imkoniyat qoʻldan boy berilganini taʼkidlaydi: Oldinroq aytganingda, men ham borgan boʻlardim.
+Xulosa: -sa edi — istak yoki «если бы» maʼnosidagi shart; -ar edi — «я бы сделал»; -gan boʻlardi — «тогда сделал бы, но не сделал».
+Bu uch shaklni bir-biridan farqlash uchun yordamchi soʻzga qarang: -sa dan keyin edi kelsa — istak yoki shart, -r/-ar dan keyin edi kelsa — natija, -gan dan keyin boʻlardi kelsa — oʻtmishdagi natija.
+Misollar:
+Pulim boʻlsa edi, uy olar edim.
+Oʻzbek tilini yaxshi bilsam edi!
+Sen kelsang edi, xursand boʻlar edim.
+Bu kitobni oʻqisangiz edi, sizga yoqar edi.
+Ertaroq chiqqanimizda, poyezdga ulgurgan boʻlardik.
+Bunday demasam edi.</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>Uzbek has no separate word for «would». Its meanings are conveyed by compound forms with the auxiliary edi or boʻlardi.
+1. A wish: -sa edi. Stem + -sa + personal ending + edi. The form expresses a dream or a regret: «if only…», «if…».
+men borsam edi — if only I went
+sen borsang edi — if only you went
+u borsa edi — if only he/she went
+biz borsak edi — if only we went
+siz borsangiz edi — if only you (pl./polite) went
+ular borsalar edi — if only they went
+Vowel stem: oʻqisam edi. Negative: bormasam edi — «I wish I hadn't gone, if only I didn't go». In speech it is often run together: borsaydim. The same form serves as an unreal condition: Vaqtim boʻlsa edi, … — «If I had time, …».
+2. The assumed result: -ar edi. Stem + -r/-ar + edi with a personal ending (edim, eding, edi, edik, edingiz, edilar).
+men borar edim — I would go
+sen borar eding — you would go
+u borar edi — he/she would go
+biz borar edik — we would go
+siz borar edingiz — you (pl./polite) would go
+ular borar edilar — they would go
+Vowel stem: oʻqir edim — «I would read». Negative: bormas edim — «I wouldn't go». Together with -sa edi it forms a full unreal condition: Vaqtim boʻlsa edi, borar edim — «If I had time, I would go». Note: the same form borar edim can also mean «I used to go» (topic 25); the context tells which.
+3. An unreal result in the past: -gan boʻlardi. The -gan participle + boʻlardi with a personal ending (boʻlardim, boʻlarding, boʻlardi, boʻlardik, boʻlardingiz, boʻlardilar).
+men borgan boʻlardim — I would have gone (then)
+sen borgan boʻlarding — you would have gone
+u borgan boʻlardi — he/she would have gone
+biz borgan boʻlardik — we would have gone
+siz borgan boʻlardingiz — you (pl./polite) would have gone
+ular borgan boʻlardilar — they would have gone
+Vowel stem: oʻqigan boʻlardim. Negative: bormagan boʻlardim. The form stresses that the moment has been missed: Oldinroq aytganingda, men ham borgan boʻlardim — «If you had told me earlier, I would have gone too».
+In short: -sa edi — a wish or an «if» condition; -ar edi — «I would do»; -gan boʻlardi — «I would have done it then, but didn't».
+Examples:
+Pulim boʻlsa edi, uy olar edim. — If I had money, I would buy a house.
+Oʻzbek tilini yaxshi bilsam edi! — If only I knew Uzbek well!
+Sen kelsang edi, xursand boʻlar edim. — If you came, I would be glad.
+Bu kitobni oʻqisangiz edi, sizga yoqar edi. — If you read this book, you would like it.
+Ertaroq chiqqanimizda, poyezdga ulgurgan boʻlardik. — If we had left earlier, we would have caught the train.
+Bunday demasam edi. — I wish I hadn't said that.</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте формы -sa edi, -ar edi и -gan boʻlardi во всех лицах от глагола kelmoq (утвердительные и отрицательные).</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>Kelmoq feʼlidan barcha shaxslarda -sa edi, -ar edi va -gan boʻlardi shakllarini yasang (boʻlishli va boʻlishsiz).</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>Form -sa edi, -ar edi and -gan boʻlardi in all persons from kelmoq (affirmative and negative).</t>
+        </is>
+      </c>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t>Превратите реальное условие в нереальное: Vaqtim boʻlsa, boraman → Vaqtim boʻlsa edi, borar edim. Pulim boʻlsa, mashina olaman. Siz kelsangiz, xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="N28" s="0" t="inlineStr">
+        <is>
+          <t>Real shartni real boʻlmagan shartga aylantiring: Vaqtim boʻlsa, boraman → Vaqtim boʻlsa edi, borar edim. Pulim boʻlsa, mashina olaman. Siz kelsangiz, xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="O28" s="0" t="inlineStr">
+        <is>
+          <t>Turn a real condition into an unreal one: Vaqtim boʻlsa, boraman → Vaqtim boʻlsa edi, borar edim. Pulim boʻlsa, mashina olaman. Siz kelsangiz, xursand boʻlaman.</t>
+        </is>
+      </c>
+      <c r="P28" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Вот бы завтра была хорошая погода! Если бы я знал, я бы помог. Если бы ты пришёл вчера, ты бы увидел его.</t>
+        </is>
+      </c>
+      <c r="Q28" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Ertaga havo yaxshi boʻlsa edi! Bilsam edi, yordam berar edim. Kecha kelganingda, uni koʻrgan boʻlarding.</t>
+        </is>
+      </c>
+      <c r="R28" s="0" t="inlineStr">
+        <is>
+          <t>Translate: If only the weather were good tomorrow! If I knew, I would help. If you had come yesterday, you would have seen him.</t>
+        </is>
+      </c>
+      <c r="S28" s="0" t="inlineStr">
+        <is>
+          <t>Напишите пять своих желаний по образцу: Oʻzbek tilini yaxshi bilsam edi!</t>
+        </is>
+      </c>
+      <c r="T28" s="0" t="inlineStr">
+        <is>
+          <t>Namunadagidek oʻzingizning beshta istagingizni yozing: Oʻzbek tilini yaxshi bilsam edi!</t>
+        </is>
+      </c>
+      <c r="U28" s="0" t="inlineStr">
+        <is>
+          <t>Write five wishes of your own following the model: Oʻzbek tilini yaxshi bilsam edi!</t>
+        </is>
+      </c>
+      <c r="V28" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог «Если бы я жил в Ташкенте…»: собеседники по очереди говорят, что бы они делали (формы -sa edi и -ar edi).</t>
+        </is>
+      </c>
+      <c r="W28" s="0" t="inlineStr">
+        <is>
+          <t>«Toshkentda yashasam edi…» mavzusida suhbat tuzing: suhbatdoshlar navbat bilan nima qilishlarini aytadi (-sa edi va -ar edi shakllari).</t>
+        </is>
+      </c>
+      <c r="X28" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue «If I lived in Tashkent…»: the speakers take turns saying what they would do (the -sa edi and -ar edi forms).</t>
+        </is>
+      </c>
+      <c r="Y28" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="10">
+      <c r="A29" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>Сложные формы прошедшего времени (-ayotgan edi, -ar edi, -gan edi)</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>Вспомогательный глагол edi («был») образует три сложных прошедших времени. Прошедшее длительное -ayotgan edi описывает действие, которое шло в определённый момент: borayotgan edim — «я шёл (тогда)». Прошедшее привычное -ar edi говорит о повторявшемся действии: borar edim — «бывало, я ходил». Давнопрошедшее -gan edi сообщает, что действие совершилось раньше другого момента в прошлом: borgan edim — «я уже ходил (тогда)».</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>Edi yordamchi feʼli oʻtgan zamonning uchta tarkibli shaklini hosil qiladi. Oʻtgan zamon davom feʼli -ayotgan edi muayyan paytda davom etayotgan harakatni bildiradi: borayotgan edim. Oʻtgan zamon odat feʼli -ar edi takrorlanib turgan harakatni bildiradi: borar edim. Uzoq oʻtgan zamon -gan edi harakat oʻtmishdagi boshqa paytdan oldin bajarilganini bildiradi: borgan edim.</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>The auxiliary edi («was») forms three compound past tenses. The past continuous -ayotgan edi describes an action that was in progress at a certain moment: borayotgan edim — «I was going (then)». The past habitual -ar edi speaks of a repeated action: borar edim — «I used to go». The pluperfect -gan edi says that the action was completed before another moment in the past: borgan edim — «I had already gone (by then)».</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>Простое прошедшее на -di (bordim) лишь сообщает факт. Чтобы показать, как действие связано с другим моментом прошлого, используются формы с edi. Личный аффикс присоединяется к edi: edim, eding, edi, edik, edingiz, edilar.
+1. Прошедшее длительное (oʻtgan zamon davom feʼli): основа + -ayotgan (после согласного) или -yotgan (после гласного) + edi. Действие было в процессе, когда произошло что-то другое.
+men borayotgan edim — я шёл
+sen borayotgan eding — ты шёл
+u borayotgan edi — он шёл
+biz borayotgan edik — мы шли
+siz borayotgan edingiz — вы шли
+ular borayotgan edilar — они шли
+Основа на гласный: oʻqiyotgan edim — «я читал (в тот момент)». Отрицание: bormayotgan edim, oʻqimayotgan edim.
+Пример: Siz qoʻngʻiroq qilganingizda, men kitob oʻqiyotgan edim — «Когда вы позвонили, я читал книгу».
+2. Прошедшее привычное (oʻtgan zamon odat feʼli): основа + -r/-ar + edi. Так рассказывают о том, что повторялось регулярно, особенно в воспоминаниях.
+men borar edim — бывало, я ходил
+sen borar eding — бывало, ты ходил
+u borar edi — бывало, он ходил
+biz borar edik — бывало, мы ходили
+siz borar edingiz — бывало, вы ходили
+ular borar edilar — бывало, они ходили
+Основа на гласный: oʻqir edim. Отрицание: bormas edim, oʻqimas edim — «бывало, не ходил / не читал». В другом контексте та же форма значит «я бы пошёл» (тема 24).
+Пример: Bolaligimda har yozda qishloqqa borar edim — «В детстве я каждое лето ездил в деревню».
+3. Давнопрошедшее (uzoq oʻtgan zamon): причастие на -gan + edi. Действие завершилось раньше другого прошедшего события.
+men borgan edim — я уже ходил (тогда)
+sen borgan eding — ты уже ходил
+u borgan edi — он уже ходил
+biz borgan edik — мы уже ходили
+siz borgan edingiz — вы уже ходили
+ular borgan edilar — они уже ходили
+Основа на гласный: oʻqigan edim. Отрицание: bormagan edim, oʻqimagan edim. После k и q аффикс -gan звучит как -kan, -qan: ekkan edim, chiqqan edim.
+Пример: Men kelganimda, ular ketgan edi — «Когда я пришёл, они уже ушли».
+Примеры:
+Kecha soat oltida biz ovqatlanayotgan edik. — Вчера в шесть часов мы ужинали.
+Yomgʻir yogʻayotgan edi. — Шёл дождь.
+Bobom har kuni ertalab gazeta oʻqir edi. — Дедушка каждое утро читал газету.
+Talabalik yillarimda koʻp sayohat qilar edim. — В студенческие годы я много путешествовал.
+Poyezd allaqachon joʻnab ketgan edi. — Поезд уже ушёл.
+Men bu filmni avval koʻrmagan edim. — Я раньше не видел этот фильм.</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>-di bilan yasalgan oddiy oʻtgan zamon (bordim) faqat faktni xabar qiladi. Harakatning oʻtmishdagi boshqa payt bilan bogʻliqligini koʻrsatish uchun edi ishtirok etgan shakllar qoʻllanadi. Shaxs-son qoʻshimchasi edi ga qoʻshiladi: edim, eding, edi, edik, edingiz, edilar.
+1. Oʻtgan zamon davom feʼli: negiz + -ayotgan (undoshdan keyin) yoki -yotgan (unlidan keyin) + edi. Boshqa voqea yuz bergan paytda harakat davom etayotgan boʻladi.
+men borayotgan edim
+sen borayotgan eding
+u borayotgan edi
+biz borayotgan edik
+siz borayotgan edingiz
+ular borayotgan edilar
+Unli bilan tugagan negiz: oʻqiyotgan edim. Boʻlishsiz shakli: bormayotgan edim, oʻqimayotgan edim.
+Misol: Siz qoʻngʻiroq qilganingizda, men kitob oʻqiyotgan edim.
+2. Oʻtgan zamon odat feʼli: negiz + -r/-ar + edi. Muntazam takrorlanib turgan ishlar, ayniqsa xotiralar shu shaklda hikoya qilinadi.
+men borar edim
+sen borar eding
+u borar edi
+biz borar edik
+siz borar edingiz
+ular borar edilar
+Unli bilan tugagan negiz: oʻqir edim. Boʻlishsiz shakli: bormas edim, oʻqimas edim. Boshqa vaziyatda shu shakl «я бы пошёл» maʼnosini beradi (24-mavzu).
+Misol: Bolaligimda har yozda qishloqqa borar edim.
+3. Uzoq oʻtgan zamon: -gan sifatdoshi + edi. Harakat oʻtmishdagi boshqa voqeadan oldin tugagan boʻladi.
+men borgan edim
+sen borgan eding
+u borgan edi
+biz borgan edik
+siz borgan edingiz
+ular borgan edilar
+Unli bilan tugagan negiz: oʻqigan edim. Boʻlishsiz shakli: bormagan edim, oʻqimagan edim. k va q dan keyin -gan qoʻshimchasi -kan, -qan tarzida boʻladi: ekkan edim, chiqqan edim.
+Misol: Men kelganimda, ular ketgan edi.
+Uch shaklni farqlash uchun edi dan oldingi qismga qarang: -ayotgan — jarayon, -r/-ar — odat, -gan — oldin tugagan harakat. Bu shakllar hikoya va xotiralarda ayniqsa koʻp uchraydi, chunki ular voqealarning ketma-ketligini aniq koʻrsatadi. Oddiy -di shakli bilan birga ishlatilganda, ular hikoyani jonli va tushunarli qiladi.
+Misollar:
+Kecha soat oltida biz ovqatlanayotgan edik.
+Yomgʻir yogʻayotgan edi.
+Bobom har kuni ertalab gazeta oʻqir edi.
+Talabalik yillarimda koʻp sayohat qilar edim.
+Poyezd allaqachon joʻnab ketgan edi.
+Men bu filmni avval koʻrmagan edim.</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>The simple -di past (bordim) only states a fact. To show how an action relates to another moment in the past, forms with edi are used. The personal ending is attached to edi: edim, eding, edi, edik, edingiz, edilar.
+1. The past continuous (oʻtgan zamon davom feʼli): stem + -ayotgan (after a consonant) or -yotgan (after a vowel) + edi. The action was in progress when something else happened.
+men borayotgan edim — I was going
+sen borayotgan eding — you were going
+u borayotgan edi — he/she was going
+biz borayotgan edik — we were going
+siz borayotgan edingiz — you (pl./polite) were going
+ular borayotgan edilar — they were going
+Vowel stem: oʻqiyotgan edim — «I was reading (at that moment)». Negative: bormayotgan edim, oʻqimayotgan edim.
+Example: Siz qoʻngʻiroq qilganingizda, men kitob oʻqiyotgan edim — «When you called, I was reading a book».
+2. The past habitual (oʻtgan zamon odat feʼli): stem + -r/-ar + edi. This is how people talk about things that happened regularly, especially in memories.
+men borar edim — I used to go
+sen borar eding — you used to go
+u borar edi — he/she used to go
+biz borar edik — we used to go
+siz borar edingiz — you (pl./polite) used to go
+ular borar edilar — they used to go
+Vowel stem: oʻqir edim. Negative: bormas edim, oʻqimas edim — «I didn't use to go / read». In another context the same form means «I would go» (topic 24).
+Example: Bolaligimda har yozda qishloqqa borar edim — «As a child I used to go to the village every summer».
+3. The pluperfect (uzoq oʻtgan zamon): the -gan participle + edi. The action was completed before another past event.
+men borgan edim — I had (already) gone
+sen borgan eding — you had gone
+u borgan edi — he/she had gone
+biz borgan edik — we had gone
+siz borgan edingiz — you (pl./polite) had gone
+ular borgan edilar — they had gone
+Vowel stem: oʻqigan edim. Negative: bormagan edim, oʻqimagan edim. After k and q the suffix -gan becomes -kan, -qan: ekkan edim, chiqqan edim.
+Example: Men kelganimda, ular ketgan edi — «When I came, they had already left».
+Examples:
+Kecha soat oltida biz ovqatlanayotgan edik. — Yesterday at six we were having dinner.
+Yomgʻir yogʻayotgan edi. — It was raining.
+Bobom har kuni ertalab gazeta oʻqir edi. — My grandfather used to read the newspaper every morning.
+Talabalik yillarimda koʻp sayohat qilar edim. — In my student years I used to travel a lot.
+Poyezd allaqachon joʻnab ketgan edi. — The train had already left.
+Men bu filmni avval koʻrmagan edim. — I had not seen this film before.</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте от глагола yozmoq все три сложные формы прошедшего времени во всех лицах (утвердительные и отрицательные).</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>Yozmoq feʼlidan oʻtgan zamonning uchala tarkibli shaklini barcha shaxslarda yasang (boʻlishli va boʻlishsiz).</t>
+        </is>
+      </c>
+      <c r="L29" s="0" t="inlineStr">
+        <is>
+          <t>Form all three compound past tenses of yozmoq in all persons (affirmative and negative).</t>
+        </is>
+      </c>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t>Выберите нужную форму: Men kelganimda, u (uxlayotgan edi / uxlagan edi). Bolaligimda koʻp (oʻynar edim / oʻynayotgan edim). Biz yetib kelganimizda, kino (boshlangan edi / boshlanar edi).</t>
+        </is>
+      </c>
+      <c r="N29" s="0" t="inlineStr">
+        <is>
+          <t>Kerakli shaklni tanlang: Men kelganimda, u (uxlayotgan edi / uxlagan edi). Bolaligimda koʻp (oʻynar edim / oʻynayotgan edim). Biz yetib kelganimizda, kino (boshlangan edi / boshlanar edi).</t>
+        </is>
+      </c>
+      <c r="O29" s="0" t="inlineStr">
+        <is>
+          <t>Choose the right form: Men kelganimda, u (uxlayotgan edi / uxlagan edi). Bolaligimda koʻp (oʻynar edim / oʻynayotgan edim). Biz yetib kelganimizda, kino (boshlangan edi / boshlanar edi).</t>
+        </is>
+      </c>
+      <c r="P29" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Когда ты позвонил, я ужинал. В детстве я каждый день читал книги. Когда мы пришли, поезд уже ушёл.</t>
+        </is>
+      </c>
+      <c r="Q29" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Sen qoʻngʻiroq qilganingda, men ovqatlanayotgan edim. Bolaligimda har kuni kitob oʻqir edim. Biz kelganimizda, poyezd ketgan edi.</t>
+        </is>
+      </c>
+      <c r="R29" s="0" t="inlineStr">
+        <is>
+          <t>Translate: When you called, I was having dinner. As a child I used to read books every day. When we arrived, the train had already left.</t>
+        </is>
+      </c>
+      <c r="S29" s="0" t="inlineStr">
+        <is>
+          <t>Поставьте в отрицание: Men gazeta oʻqir edim. U uxlayotgan edi. Biz bu shaharni koʻrgan edik.</t>
+        </is>
+      </c>
+      <c r="T29" s="0" t="inlineStr">
+        <is>
+          <t>Boʻlishsiz shaklga qoʻying: Men gazeta oʻqir edim. U uxlayotgan edi. Biz bu shaharni koʻrgan edik.</t>
+        </is>
+      </c>
+      <c r="U29" s="0" t="inlineStr">
+        <is>
+          <t>Make negative: Men gazeta oʻqir edim. U uxlayotgan edi. Biz bu shaharni koʻrgan edik.</t>
+        </is>
+      </c>
+      <c r="V29" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог «Детство»: собеседники рассказывают, что они делали каждое лето (форма -ar edi) и что делали в какой-то конкретный момент (форма -ayotgan edi).</t>
+        </is>
+      </c>
+      <c r="W29" s="0" t="inlineStr">
+        <is>
+          <t>«Bolalik» mavzusida suhbat tuzing: suhbatdoshlar har yozda nima qilishganini (-ar edi shakli) va muayyan bir paytda nima qilayotganini (-ayotgan edi shakli) aytib beradi.</t>
+        </is>
+      </c>
+      <c r="X29" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue «Childhood»: the speakers tell what they used to do every summer (the -ar edi form) and what they were doing at a particular moment (the -ayotgan edi form).</t>
+        </is>
+      </c>
+      <c r="Y29" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="10">
+      <c r="A30" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>Возможность: -a/-y olmoq и -sh mumkin</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>Способность что-либо сделать выражается сочетанием формы на -a/-y с глаголом olmoq: bora olaman — «я могу пойти», oʻqiy olaman — «я могу прочитать». Спрягается только olmoq, и отрицание тоже ставится на него: bora olmayman — «я не могу пойти». Безличная возможность или разрешение выражается конструкцией -sh mumkin: borish mumkin — «можно пойти», borish mumkin emas — «нельзя пойти».</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>Biror ishni bajara olish -a/-y shaklidagi ravishdosh va olmoq feʼli birikmasi bilan ifodalanadi: bora olaman, oʻqiy olaman. Faqat olmoq feʼli tuslanadi, boʻlishsizlik ham unga qoʻshiladi: bora olmayman. Shaxssiz imkoniyat yoki ruxsat -sh mumkin qurilmasi bilan ifodalanadi: borish mumkin, borish mumkin emas.</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>The ability to do something is expressed by the -a/-y form combined with the verb olmoq: bora olaman — «I can go», oʻqiy olaman — «I can read». Only olmoq is conjugated, and the negative goes on it too: bora olmayman — «I can't go». Impersonal possibility or permission is expressed by the -sh mumkin construction: borish mumkin — «one may go», borish mumkin emas — «one may not go».</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>Русское «могу» передаёт и умение, и физическую возможность, и разрешение. В узбекском для этого есть две основные конструкции.
+1. -a/-y olmoq — «мочь, быть в состоянии». К основе присоединяется -a (после согласного) или -y (после гласного), затем ставится глагол olmoq, который и спрягается: bor- → bora olmoq, oʻqi- → oʻqiy olmoq, ishla- → ishlay olmoq. Смысловой глагол при этом не изменяется.
+Настояще-будущее время (bormoq):
+men bora olaman — я могу пойти
+sen bora olasan — ты можешь пойти
+u bora oladi — он может пойти
+biz bora olamiz — мы можем пойти
+siz bora olasiz — вы можете пойти
+ular bora oladi(lar) — они могут пойти
+Отрицание ставится на olmoq, а не на смысловой глагол:
+men bora olmayman — я не могу пойти
+sen bora olmaysan — ты не можешь пойти
+u bora olmaydi — он не может пойти
+biz bora olmaymiz — мы не можем пойти
+siz bora olmaysiz — вы не можете пойти
+ular bora olmaydi(lar) — они не могут пойти
+Основа на гласный (oʻqimoq): oʻqiy olaman, oʻqiy olmayman. Глагол olmoq можно ставить и в другие времена: bora oldim — «я смог пойти», bora olmadim — «я не смог пойти». Вопрос с -mi звучит как вежливая просьба: Yordam bera olasizmi? — «Вы можете помочь?»
+2. -sh mumkin — «можно». Отглагольное имя на -ish (после согласного) или -sh (после гласного) + слово mumkin: borish mumkin — «можно пойти», oʻqish mumkin — «можно читать». Конструкция безличная: она говорит о возможности или разрешении вообще. Отрицание — mumkin emas: Bu yerda chekish mumkin emas — «Здесь курить нельзя».
+Чтобы указать лицо, к имени на -ish добавляют притяжательный аффикс: borishim mumkin — «я, возможно, пойду», borishingiz mumkin — «вы можете пойти». Такая форма часто означает вероятность: U kechikishi mumkin — «Он может опоздать».
+Сравните:
+Men suza olaman — «Я могу плавать» (способность).
+Bu yerda suzish mumkin — «Здесь можно плавать» (разрешение).
+Ertaga kela olmayman — «Завтра я не смогу прийти» (нет возможности).
+Ertaga kelishim mumkin — «Завтра я, может быть, приду» (вероятность).
+Примеры:
+Men oʻzbekcha gapira olaman. — Я могу говорить по-узбекски.
+Bu masalani yecha olmadim. — Я не смог решить эту задачу.
+Siz ertaga kela olasizmi? — Вы сможете прийти завтра?
+Muzeyda rasmga olish mumkin. — В музее можно фотографировать.
+Bu yerda mashina qoʻyish mumkin emas. — Здесь нельзя ставить машину.
+Bugun yomgʻir yogʻishi mumkin. — Сегодня может пойти дождь.</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>Rus tilidagi «могу» soʻzi ham mahoratni, ham jismoniy imkoniyatni, ham ruxsatni bildiradi. Oʻzbek tilida buning uchun ikki asosiy qurilma bor.
+1. -a/-y olmoq — biror ishni bajara olish. Negizga -a (undoshdan keyin) yoki -y (unlidan keyin) qoʻshiladi, soʻng olmoq feʼli keladi va aynan u tuslanadi: bor- → bora olmoq, oʻqi- → oʻqiy olmoq, ishla- → ishlay olmoq. Asosiy feʼl bunda oʻzgarmaydi.
+Hozirgi-kelasi zamon (bormoq):
+men bora olaman
+sen bora olasan
+u bora oladi
+biz bora olamiz
+siz bora olasiz
+ular bora oladi(lar)
+Boʻlishsizlik asosiy feʼlga emas, olmoq feʼliga qoʻshiladi:
+men bora olmayman
+sen bora olmaysan
+u bora olmaydi
+biz bora olmaymiz
+siz bora olmaysiz
+ular bora olmaydi(lar)
+Unli bilan tugagan negiz (oʻqimoq): oʻqiy olaman, oʻqiy olmayman. Olmoq feʼli boshqa zamonlarda ham qoʻllanadi: bora oldim, bora olmadim. -mi bilan soʻroq hurmatli iltimos boʻlib eshitiladi: Yordam bera olasizmi?
+2. -sh mumkin — ruxsat yoki imkoniyat. -ish (undoshdan keyin) yoki -sh (unlidan keyin) qoʻshimchali harakat nomi + mumkin soʻzi: borish mumkin, oʻqish mumkin. Bu qurilma shaxssiz: u umuman imkoniyat yoki ruxsat haqida gapiradi. Boʻlishsiz shakli — mumkin emas: Bu yerda chekish mumkin emas.
+Shaxsni koʻrsatish uchun -ish qoʻshimchali harakat nomiga egalik qoʻshimchasi qoʻshiladi: borishim mumkin, borishingiz mumkin. Bunday shakl koʻpincha ehtimolni bildiradi: U kechikishi mumkin.
+Taqqoslang:
+Men suza olaman — qobiliyat.
+Bu yerda suzish mumkin — ruxsat.
+Ertaga kela olmayman — imkoniyat yoʻq.
+Ertaga kelishim mumkin — ehtimol.
+Eʼtibor bering: -a/-y olmoq qurilmasida asosiy feʼl tuslanmaydi va boʻlishsiz shaklga qoʻyilmaydi; faqat bora olmayman deyiladi. -sh mumkin qurilmasida esa mumkin soʻzi oʻzgarmaydi, shaxs harakat nomidagi egalik qoʻshimchasi orqali koʻrsatiladi.
+Demak, shaxsning oʻz kuchi, mahorati haqida gap ketganda -a/-y olmoq, umumiy ruxsat, taqiq yoki ehtimol haqida gap ketganda esa -sh mumkin qurilmasi tanlanadi.
+Misollar:
+Men oʻzbekcha gapira olaman.
+Bu masalani yecha olmadim.
+Siz ertaga kela olasizmi?
+Muzeyda rasmga olish mumkin.
+Bu yerda mashina qoʻyish mumkin emas.
+Bugun yomgʻir yogʻishi mumkin.</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>The Russian «могу» covers skill, physical ability and permission alike. Uzbek has two main constructions for this.
+1. -a/-y olmoq — «to be able to». The stem takes -a (after a consonant) or -y (after a vowel), then comes the verb olmoq, which is the one conjugated: bor- → bora olmoq, oʻqi- → oʻqiy olmoq, ishla- → ishlay olmoq. The main verb itself does not change.
+Present-future (bormoq):
+men bora olaman — I can go
+sen bora olasan — you can go
+u bora oladi — he/she can go
+biz bora olamiz — we can go
+siz bora olasiz — you (pl./polite) can go
+ular bora oladi(lar) — they can go
+The negative goes on olmoq, not on the main verb:
+men bora olmayman — I can't go
+sen bora olmaysan — you can't go
+u bora olmaydi — he/she can't go
+biz bora olmaymiz — we can't go
+siz bora olmaysiz — you (pl./polite) can't go
+ular bora olmaydi(lar) — they can't go
+Vowel stem (oʻqimoq): oʻqiy olaman, oʻqiy olmayman. Olmoq can be put into other tenses as well: bora oldim — «I managed to go», bora olmadim — «I couldn't go». A question with -mi sounds like a polite request: Yordam bera olasizmi? — «Can you help?»
+2. -sh mumkin — «it is possible, one may». The verbal noun in -ish (after a consonant) or -sh (after a vowel) + the word mumkin: borish mumkin — «one may go», oʻqish mumkin — «one may read». The construction is impersonal: it speaks of possibility or permission in general. The negative is mumkin emas: Bu yerda chekish mumkin emas — «Smoking is not allowed here».
+To indicate the person, a possessive ending is added to the -ish noun: borishim mumkin — «I may go», borishingiz mumkin — «you may go». This form often expresses probability: U kechikishi mumkin — «He may be late».
+Compare:
+Men suza olaman — «I can swim» (ability).
+Bu yerda suzish mumkin — «Swimming is allowed here» (permission).
+Ertaga kela olmayman — «I can't come tomorrow» (no possibility).
+Ertaga kelishim mumkin — «I might come tomorrow» (probability).
+Examples:
+Men oʻzbekcha gapira olaman. — I can speak Uzbek.
+Bu masalani yecha olmadim. — I couldn't solve this problem.
+Siz ertaga kela olasizmi? — Can you come tomorrow?
+Muzeyda rasmga olish mumkin. — Taking photos is allowed in the museum.
+Bu yerda mashina qoʻyish mumkin emas. — You can't park here.
+Bugun yomgʻir yogʻishi mumkin. — It may rain today.</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>Образуйте формы возможности (утвердительные и отрицательные) во всех лицах от глаголов yozmoq и ishlamoq.</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>Yozmoq va ishlamoq feʼllaridan barcha shaxslarda -a/-y olmoq shaklini yasang (boʻlishli va boʻlishsiz).</t>
+        </is>
+      </c>
+      <c r="L30" s="0" t="inlineStr">
+        <is>
+          <t>Form the ability construction (affirmative and negative) in all persons from yozmoq and ishlamoq.</t>
+        </is>
+      </c>
+      <c r="M30" s="0" t="inlineStr">
+        <is>
+          <t>Поставьте в отрицание: Men suza olaman. U kela oladi. Bu yerda chekish mumkin. Biz bora oldik.</t>
+        </is>
+      </c>
+      <c r="N30" s="0" t="inlineStr">
+        <is>
+          <t>Boʻlishsiz shaklga qoʻying: Men suza olaman. U kela oladi. Bu yerda chekish mumkin. Biz bora oldik.</t>
+        </is>
+      </c>
+      <c r="O30" s="0" t="inlineStr">
+        <is>
+          <t>Make negative: Men suza olaman. U kela oladi. Bu yerda chekish mumkin. Biz bora oldik.</t>
+        </is>
+      </c>
+      <c r="P30" s="0" t="inlineStr">
+        <is>
+          <t>Переведите: Я могу говорить по-узбекски. Здесь нельзя фотографировать. Вы сможете мне помочь? Завтра может пойти снег.</t>
+        </is>
+      </c>
+      <c r="Q30" s="0" t="inlineStr">
+        <is>
+          <t>Tarjima qiling: Men oʻzbekcha gapira olaman. Bu yerda rasmga olish mumkin emas. Menga yordam bera olasizmi? Ertaga qor yogʻishi mumkin.</t>
+        </is>
+      </c>
+      <c r="R30" s="0" t="inlineStr">
+        <is>
+          <t>Translate: I can speak Uzbek. Taking photos is not allowed here. Can you help me? It may snow tomorrow.</t>
+        </is>
+      </c>
+      <c r="S30" s="0" t="inlineStr">
+        <is>
+          <t>Составьте по два предложения с -a/-y olmoq и с -sh mumkin о правилах в музее или библиотеке и объясните, почему выбрана та или иная конструкция.</t>
+        </is>
+      </c>
+      <c r="T30" s="0" t="inlineStr">
+        <is>
+          <t>Muzey yoki kutubxona qoidalari haqida -a/-y olmoq va -sh mumkin bilan ikkitadan gap tuzing va nima uchun aynan shu qurilma tanlanganini tushuntiring.</t>
+        </is>
+      </c>
+      <c r="U30" s="0" t="inlineStr">
+        <is>
+          <t>Write two sentences each with -a/-y olmoq and -sh mumkin about the rules in a museum or library, and explain why each construction was chosen.</t>
+        </is>
+      </c>
+      <c r="V30" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог: вас приглашают на встречу, а вы вежливо отказываетесь (kela olmayman) и предлагаете другой день (… kelishim mumkin).</t>
+        </is>
+      </c>
+      <c r="W30" s="0" t="inlineStr">
+        <is>
+          <t>Suhbat tuzing: sizni uchrashuvga taklif qilishadi, siz esa hurmat bilan rad etasiz (kela olmayman) va boshqa kunni taklif qilasiz (… kelishim mumkin).</t>
+        </is>
+      </c>
+      <c r="X30" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue: you are invited to a meeting, you politely decline (kela olmayman) and suggest another day (… kelishim mumkin).</t>
+        </is>
+      </c>
+      <c r="Y30" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="10">
+      <c r="A31" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>Обзор: времена и наклонения глагола</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>Узбекский глагол строится по одной схеме: основа + (отрицание -ma) + аффикс времени или наклонения + личный аффикс. Наклонения: изъявительное (времена), повелительно-желательное, условное, сослагательные формы с edi и boʻlardi, а также конструкции возможности. Отрицание обычно даёт -ma, будущее предположительное и привычное прошедшее берут -mas, а форма -moqchi отрицается словом emas. В тренажёре спряжения введите инфинитив, например bormoq, и найдите строку по узбекскому названию и аффиксу из этой таблицы.</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>Oʻzbek feʼli bir xil chizma asosida tuziladi: negiz + (boʻlishsizlik -ma) + zamon yoki mayl qoʻshimchasi + shaxs-son qoʻshimchasi. Mayllar: xabar mayli (zamonlar), buyruq-istak mayli, shart mayli, edi va boʻlardi bilan yasaladigan istak va shart-natija shakllari, shuningdek imkoniyat qurilmalari. Boʻlishsizlik odatda -ma bilan ifodalanadi, kelasi zamon gumon feʼli va oʻtgan zamon odat feʼli -mas oladi, -moqchi shakli esa emas soʻzi bilan inkor qilinadi. Tuslash mashqida feʼlning -moq shaklini, masalan bormoq ni kiriting va kerakli qatorni shu jadvaldagi oʻzbekcha nom va qoʻshimcha boʻyicha toping.</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>The Uzbek verb follows a single pattern: stem + (negative -ma) + tense or mood suffix + personal ending. The moods are: the indicative (the tenses), the imperative-optative, the conditional, the subjunctive forms with edi and boʻlardi, and the ability constructions. The negative is usually -ma, the presumptive future and the past habitual take -mas, and the -moqchi form is negated with the word emas. In the conjugation trainer, enter an infinitive such as bormoq and find the row by the Uzbek name and suffix from this table.</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>Эта тема собирает изученные формы глагола в одну таблицу. Формы даны для лица men на примере bormoq (основа на согласный) и oʻqimoq (основа на гласный); через косую черту — отрицание.
+Общая схема: основа + (-ma) + аффикс формы + личный аффикс. Личные аффиксы бывают двух типов: сказуемостные (-man, -san, —, -miz, -siz, -lar) — после -a/-y, -r/-ar, -gan, -moqchi; притяжательные (-m, -ng, —, -k, -ngiz, -lar) — после -di и -sa, а также у edi: edim, eding, edi.
+Изъявительное наклонение:
+-a/-y: boraman / bormayman; oʻqiyman / oʻqimayman — иду, пойду
+-yap: boryapman / bormayapman; oʻqiyapman — иду сейчас
+-di: bordim / bormadim; oʻqidim / oʻqimadim — пошёл, ходил
+-gan: borganman / bormaganman; oʻqiganman — ходил (бывал)
+-ayotgan edi: borayotgan edim / bormayotgan edim; oʻqiyotgan edim — шёл (в тот момент)
+-gan edi: borgan edim / bormagan edim; oʻqigan edim — уже ходил (тогда)
+-ar edi: borar edim / bormas edim; oʻqir edim — бывало, ходил
+-r/-ar: borarman / bormasman; oʻqirman / oʻqimasman — наверное, пойду
+-moqchi: bormoqchiman / bormoqchi emasman; oʻqimoqchiman — собираюсь пойти
+Повелительно-желательное наклонение: boray — пойду-ка я; bor / borma — иди / не ходи; borsin — пусть идёт; boraylik — пойдём; boring / bormang — идите / не ходите; oʻqi / oʻqima; oʻqing / oʻqimang.
+Условное наклонение:
+-sa: borsam / bormasam; oʻqisam / oʻqimasam — если пойду
+Сослагательные формы:
+-sa edi: borsam edi / bormasam edi; oʻqisam edi — вот бы я пошёл
+-ar edi: borar edim / bormas edim — я бы пошёл
+-gan boʻlardi: borgan boʻlardim / bormagan boʻlardim; oʻqigan boʻlardim — я бы пошёл (тогда)
+Возможность:
+-a/-y olmoq: bora olaman / bora olmayman; oʻqiy olaman / oʻqiy olmayman — могу пойти
+-sh mumkin: borish mumkin / borish mumkin emas; oʻqish mumkin — можно пойти
+Как запомнить отрицание. Обычно -ma ставится сразу после основы: bor-ma-dim, bor-ma-sa, bor-ma-gan. Исключения: будущее предположительное и привычное прошедшее берут -mas (bormasman, bormas edim); у -moqchi и mumkin отрицание — emas; у -a olmoq отрицается olmoq (bora olmayman).
+Как найти форму в тренажёре спряжения. Введите глагол в инфинитиве на -moq (bormoq, oʻqimoq). Тренажёр покажет формы по группам: изъявительное наклонение, повелительно-желательное, условное и сослагательное, возможность, а затем неличные формы. Каждая строка подписана узбекским названием и аффиксом, например «Kelasi zamon gumon (-r / -ar)» или «Shart mayli (-sa)». Форму -ar edi в значении «я бы пошёл» ищите в строке «Oʻtgan zamon odat (-ar edi)», а имя на -ish для -sh mumkin — среди неличных форм (Harakat nomi). Если ошиблись, повторите тему этой формы.
+Примеры:
+Har kuni ishga boraman. — Каждый день хожу на работу.
+Hozir kitob oʻqiyapman. — Сейчас я читаю книгу.
+Ertaga bozorga bormoqchiman. — Завтра собираюсь на базар.
+Vaqtim boʻlsa, borarman. — Если будет время, наверное, пойду.
+Bolaligimda koʻp kitob oʻqir edim. — В детстве я, бывало, много читал.
+Afsuski, bora olmadim. — К сожалению, я не смог пойти.</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>Bu mavzu oʻrganilgan feʼl shakllarini bitta jadvalga jamlaydi. Shakllar men shaxsi uchun bormoq (undosh bilan tugagan negiz) va oʻqimoq (unli bilan tugagan negiz) misolida berilgan; qiya chiziqdan keyin — boʻlishsiz shakl.
+Umumiy chizma: negiz + (-ma) + shakl qoʻshimchasi + shaxs-son qoʻshimchasi. Shaxs-son qoʻshimchalari ikki xil: kesimlik qoʻshimchalari (-man, -san, —, -miz, -siz, -lar) — -a/-y, -r/-ar, -gan, -moqchi dan keyin; egalik tipidagi qoʻshimchalar (-m, -ng, —, -k, -ngiz, -lar) — -di va -sa dan keyin, shuningdek edi da: edim, eding, edi.
+Xabar mayli:
+-a/-y: boraman / bormayman; oʻqiyman / oʻqimayman
+-yap: boryapman / bormayapman; oʻqiyapman
+-di: bordim / bormadim; oʻqidim / oʻqimadim
+-gan: borganman / bormaganman; oʻqiganman
+-ayotgan edi: borayotgan edim / bormayotgan edim; oʻqiyotgan edim
+-gan edi: borgan edim / bormagan edim; oʻqigan edim
+-ar edi: borar edim / bormas edim; oʻqir edim
+-r/-ar: borarman / bormasman; oʻqirman / oʻqimasman
+-moqchi: bormoqchiman / bormoqchi emasman; oʻqimoqchiman
+Buyruq-istak mayli: boray; bor / borma; borsin; boraylik; boring / bormang; oʻqi / oʻqima; oʻqing / oʻqimang.
+Shart mayli:
+-sa: borsam / bormasam; oʻqisam / oʻqimasam
+Istak va shart-natija shakllari:
+-sa edi: borsam edi / bormasam edi; oʻqisam edi
+-ar edi: borar edim / bormas edim
+-gan boʻlardi: borgan boʻlardim / bormagan boʻlardim; oʻqigan boʻlardim
+Imkoniyat:
+-a/-y olmoq: bora olaman / bora olmayman; oʻqiy olaman / oʻqiy olmayman
+-sh mumkin: borish mumkin / borish mumkin emas; oʻqish mumkin
+Boʻlishsizlikni qanday eslab qolish mumkin. Odatda -ma negizdan keyin darhol keladi: bor-ma-dim, bor-ma-sa, bor-ma-gan. Istisnolar: kelasi zamon gumon feʼli va oʻtgan zamon odat feʼli -mas oladi (bormasman, bormas edim); -moqchi va mumkin da inkor — emas; -a olmoq da olmoq inkor qilinadi (bora olmayman).
+Tuslash mashqida shaklni qanday topish mumkin. Feʼlni -moq bilan tugagan shaklda kiriting (bormoq, oʻqimoq). Mashq shakllarni guruhlarga ajratib koʻrsatadi: xabar mayli, buyruq-istak mayli, shart mayli va istak shakllari, imkoniyat, soʻng vazifa shakllari. Har bir qator oʻzbekcha nom va qoʻshimcha bilan belgilangan, masalan «Kelasi zamon gumon (-r / -ar)» yoki «Shart mayli (-sa)». «Я бы пошёл» maʼnosidagi -ar edi shaklini «Oʻtgan zamon odat (-ar edi)» qatoridan, -sh mumkin uchun -ish qoʻshimchali harakat nomini esa vazifa shakllari orasidan (Harakat nomi) qidiring. Xato qilsangiz, shu shaklga bagʻishlangan mavzuni takrorlang.
+Misollar:
+Har kuni ishga boraman.
+Hozir kitob oʻqiyapman.
+Ertaga bozorga bormoqchiman.
+Vaqtim boʻlsa, borarman.
+Bolaligimda koʻp kitob oʻqir edim.
+Afsuski, bora olmadim.</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>This topic gathers the studied verb forms into one table, for men, using bormoq (consonant stem) and oʻqimoq (vowel stem); after the slash comes the negative.
+General pattern: stem + (-ma) + form suffix + personal ending. Predicative endings (-man, -san, —, -miz, -siz, -lar) follow -a/-y, -r/-ar, -gan, -moqchi; possessive-type endings (-m, -ng, —, -k, -ngiz, -lar) follow -di and -sa and attach to edi: edim, eding, edi.
+Indicative mood:
+-a/-y: boraman / bormayman; oʻqiyman / oʻqimayman — I go, I will go
+-yap: boryapman / bormayapman; oʻqiyapman — I am going now
+-di: bordim / bormadim; oʻqidim / oʻqimadim — I went
+-gan: borganman / bormaganman; oʻqiganman — I have gone (been)
+-ayotgan edi: borayotgan edim / bormayotgan edim; oʻqiyotgan edim — I was going (at that moment)
+-gan edi: borgan edim / bormagan edim; oʻqigan edim — I had already gone (by then)
+-ar edi: borar edim / bormas edim; oʻqir edim — I used to go
+-r/-ar: borarman / bormasman; oʻqirman / oʻqimasman — I will probably go
+-moqchi: bormoqchiman / bormoqchi emasman; oʻqimoqchiman — I am going to go
+Imperative-optative mood: boray — let me go; bor / borma — go / don't go; borsin — let him go; boraylik — let's go; boring / bormang — go / don't go (polite); oʻqi / oʻqima; oʻqing / oʻqimang.
+Conditional mood:
+-sa: borsam / bormasam; oʻqisam / oʻqimasam — if I go
+Subjunctive forms:
+-sa edi: borsam edi / bormasam edi; oʻqisam edi — if only I went
+-ar edi: borar edim / bormas edim — I would go
+-gan boʻlardi: borgan boʻlardim / bormagan boʻlardim; oʻqigan boʻlardim — I would have gone (then)
+Ability and possibility:
+-a/-y olmoq: bora olaman / bora olmayman; oʻqiy olaman / oʻqiy olmayman — I can go
+-sh mumkin: borish mumkin / borish mumkin emas; oʻqish mumkin — one may go
+Negation. Usually -ma follows the stem: bor-ma-dim, bor-ma-sa, bor-ma-gan. Exceptions: the presumptive future and the past habitual take -mas (bormasman, bormas edim); -moqchi and mumkin are negated with emas; in -a olmoq it is olmoq that is negated (bora olmayman).
+The conjugation trainer. Enter a -moq infinitive (bormoq, oʻqimoq). The forms are grouped by mood, followed by the non-finite forms. Each row is labelled with an Uzbek name and a suffix, for example «Kelasi zamon gumon (-r / -ar)» or «Shart mayli (-sa)». The «would» sense of -ar edi is in the row «Oʻtgan zamon odat (-ar edi)»; the -ish noun for -sh mumkin is under Harakat nomi.
+Examples:
+Har kuni ishga boraman. — I go to work every day.
+Hozir kitob oʻqiyapman. — I am reading a book now.
+Ertaga bozorga bormoqchiman. — Tomorrow I am going to go to the bazaar.
+Vaqtim boʻlsa, borarman. — If I have time, I'll probably go.
+Bolaligimda koʻp kitob oʻqir edim. — As a child I used to read a lot of books.
+Afsuski, bora olmadim. — Unfortunately, I couldn't go.</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>Заполните таблицу для глагола kelmoq: для лица men образуйте все формы из обзорной таблицы (утвердительные и отрицательные), затем проверьте себя в тренажёре спряжения.</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>Kelmoq feʼli uchun jadvalni toʻldiring: men shaxsi uchun takrorlash jadvalidagi barcha shakllarni yasang (boʻlishli va boʻlishsiz), soʻng tuslash mashqida oʻzingizni tekshiring.</t>
+        </is>
+      </c>
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>Fill in the table for kelmoq: form every form from the review table for men (affirmative and negative), then check yourself in the conjugation trainer.</t>
+        </is>
+      </c>
+      <c r="M31" s="0" t="inlineStr">
+        <is>
+          <t>Определите время или наклонение: bormoqchiman, oʻqir edim, borsam edi, bora olmayman, oʻqiyotgan edim, borgan boʻlardim, bormasman.</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
+        <is>
+          <t>Zamon yoki maylni aniqlang: bormoqchiman, oʻqir edim, borsam edi, bora olmayman, oʻqiyotgan edim, borgan boʻlardim, bormasman.</t>
+        </is>
+      </c>
+      <c r="O31" s="0" t="inlineStr">
+        <is>
+          <t>Identify the tense or mood: bormoqchiman, oʻqir edim, borsam edi, bora olmayman, oʻqiyotgan edim, borgan boʻlardim, bormasman.</t>
+        </is>
+      </c>
+      <c r="P31" s="0" t="inlineStr">
+        <is>
+          <t>Поставьте в отрицание и объясните, каким способом оно образовано: borarman, bormoqchiman, bora olaman, borish mumkin, borsam, borar edim.</t>
+        </is>
+      </c>
+      <c r="Q31" s="0" t="inlineStr">
+        <is>
+          <t>Boʻlishsiz shaklga qoʻying va qanday yasalganini tushuntiring: borarman, bormoqchiman, bora olaman, borish mumkin, borsam, borar edim.</t>
+        </is>
+      </c>
+      <c r="R31" s="0" t="inlineStr">
+        <is>
+          <t>Make negative and explain how each negative is formed: borarman, bormoqchiman, bora olaman, borish mumkin, borsam, borar edim.</t>
+        </is>
+      </c>
+      <c r="S31" s="0" t="inlineStr">
+        <is>
+          <t>Переведите, выбирая нужную форму: Я, наверное, приду. Я собираюсь прийти. Если я приду… Вот бы мне прийти! Я не могу прийти. Бывало, я приходил.</t>
+        </is>
+      </c>
+      <c r="T31" s="0" t="inlineStr">
+        <is>
+          <t>Kerakli shaklni tanlab tarjima qiling: Ehtimol, kelarman. Kelmoqchiman. Kelsam… Kelsam edi! Kela olmayman. Kelar edim.</t>
+        </is>
+      </c>
+      <c r="U31" s="0" t="inlineStr">
+        <is>
+          <t>Translate, choosing the right form: I'll probably come. I'm going to come. If I come… If only I could come! I can't come. I used to come.</t>
+        </is>
+      </c>
+      <c r="V31" s="0" t="inlineStr">
+        <is>
+          <t>Составьте диалог «Планы и мечты» из 8–10 реплик, в котором встречаются не менее пяти разных форм из обзорной таблицы.</t>
+        </is>
+      </c>
+      <c r="W31" s="0" t="inlineStr">
+        <is>
+          <t>«Rejalar va orzular» mavzusida 8–10 ta gapdan iborat suhbat tuzing; unda takrorlash jadvalidagi kamida beshta turli shakl qatnashsin.</t>
+        </is>
+      </c>
+      <c r="X31" s="0" t="inlineStr">
+        <is>
+          <t>Write a dialogue «Plans and dreams» of 8–10 lines that uses at least five different forms from the review table.</t>
+        </is>
+      </c>
+      <c r="Y31" s="0" t="inlineStr">
+        <is>
+          <t>Учебные пособия по узбекской грамматике (общие правила литературного языка)</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1" s="10"/>
     <row r="33" ht="15.75" customHeight="1" s="10"/>
     <row r="34" ht="15.75" customHeight="1" s="10"/>
